--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.21264893234513</v>
+        <v>3.934555451506084</v>
       </c>
       <c r="D2" t="n">
-        <v>25.62018086704115</v>
+        <v>4.163279390894187</v>
       </c>
       <c r="E2" t="n">
-        <v>10.62133655701366</v>
+        <v>1.72596719051472</v>
       </c>
       <c r="F2" t="n">
-        <v>7.29835820520082</v>
+        <v>1.185983208345133</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.384719771121078</v>
+        <v>1.200016962807175</v>
       </c>
       <c r="D3" t="n">
-        <v>9.515621480186935</v>
+        <v>1.546288490530377</v>
       </c>
       <c r="E3" t="n">
-        <v>10.62133655701366</v>
+        <v>1.72596719051472</v>
       </c>
       <c r="F3" t="n">
-        <v>7.29835820520082</v>
+        <v>1.185983208345133</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.073036140132843</v>
+        <v>0.499368372771587</v>
       </c>
       <c r="D4" t="n">
-        <v>4.60066297105565</v>
+        <v>0.7476077327965431</v>
       </c>
       <c r="E4" t="n">
-        <v>10.62133655701366</v>
+        <v>1.72596719051472</v>
       </c>
       <c r="F4" t="n">
-        <v>7.29835820520082</v>
+        <v>1.185983208345133</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.57686477558335</v>
+        <v>1.881240526032295</v>
       </c>
       <c r="D5" t="n">
-        <v>10.94028835529722</v>
+        <v>1.777796857735799</v>
       </c>
       <c r="E5" t="n">
-        <v>10.62133655701366</v>
+        <v>1.72596719051472</v>
       </c>
       <c r="F5" t="n">
-        <v>7.29835820520082</v>
+        <v>1.185983208345133</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.38959572601791</v>
+        <v>5.10080930547791</v>
       </c>
       <c r="D6" t="n">
-        <v>17.73954026712329</v>
+        <v>2.882675293407534</v>
       </c>
       <c r="E6" t="n">
-        <v>10.62133655701366</v>
+        <v>1.72596719051472</v>
       </c>
       <c r="F6" t="n">
-        <v>7.29835820520082</v>
+        <v>1.185983208345133</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
